--- a/kahoot/orientation/finnish-history/main-periods-of-finnish-history-2-independent-finland__0006.xlsx
+++ b/kahoot/orientation/finnish-history/main-periods-of-finnish-history-2-independent-finland__0006.xlsx
@@ -1835,17 +1835,17 @@
       </c>
       <c r="D9" s="14" t="inlineStr">
         <is>
-          <t>För att slippa skatter</t>
+          <t>För att stärka Finlands ställning i EU</t>
         </is>
       </c>
       <c r="E9" s="14" t="inlineStr">
         <is>
-          <t>För att byta valuta</t>
+          <t>För att fördjupa säkerhetssamarbetet i Norden</t>
         </is>
       </c>
       <c r="F9" s="14" t="inlineStr">
         <is>
-          <t>För att stoppa utbildning</t>
+          <t>För att markera tydligare västlig inriktning</t>
         </is>
       </c>
       <c r="G9" s="14" t="n">
@@ -1892,17 +1892,17 @@
       </c>
       <c r="D10" s="14" t="inlineStr">
         <is>
-          <t>Finland lämnar Europa</t>
+          <t>Finland kan delta i Natos planering och övningar</t>
         </is>
       </c>
       <c r="E10" s="14" t="inlineStr">
         <is>
-          <t>Finland avskaffar armén</t>
+          <t>Finland får fördjupat säkerhetssamarbete i Norden</t>
         </is>
       </c>
       <c r="F10" s="14" t="inlineStr">
         <is>
-          <t>Finland blir neutralt igen</t>
+          <t>Finland får större avskräckande effekt</t>
         </is>
       </c>
       <c r="G10" s="14" t="n">
@@ -1949,17 +1949,17 @@
       </c>
       <c r="D11" s="21" t="inlineStr">
         <is>
-          <t>Ingen medlem hjälper någon</t>
+          <t>Hjälp beslutas från fall till fall</t>
         </is>
       </c>
       <c r="E11" s="14" t="inlineStr">
         <is>
-          <t>Bara stora länder hjälper</t>
+          <t>Garantier gäller främst politiskt stöd</t>
         </is>
       </c>
       <c r="F11" s="14" t="inlineStr">
         <is>
-          <t>Garantier gäller bara ekonomi</t>
+          <t>Garantier gäller främst inom EU-samarbetet</t>
         </is>
       </c>
       <c r="G11" s="14" t="n">
@@ -2063,17 +2063,17 @@
       </c>
       <c r="D13" s="14" t="inlineStr">
         <is>
-          <t>Genom att avskaffa försvaret</t>
+          <t>Genom Partnerskap för fred</t>
         </is>
       </c>
       <c r="E13" s="14" t="inlineStr">
         <is>
-          <t>Genom att byta språk</t>
+          <t>Genom Nato-ledd krishantering</t>
         </is>
       </c>
       <c r="F13" s="14" t="inlineStr">
         <is>
-          <t>Genom att stänga gränser</t>
+          <t>Genom nordiskt försvarssamarbete</t>
         </is>
       </c>
       <c r="G13" s="14" t="n">
@@ -2115,7 +2115,7 @@
       </c>
       <c r="C14" s="14" t="inlineStr">
         <is>
-          <t>1995</t>
+          <t>1917</t>
         </is>
       </c>
       <c r="D14" s="14" t="inlineStr">
@@ -2125,12 +2125,12 @@
       </c>
       <c r="E14" s="14" t="inlineStr">
         <is>
-          <t>2023</t>
+          <t>2007</t>
         </is>
       </c>
       <c r="F14" s="14" t="inlineStr">
         <is>
-          <t>1939</t>
+          <t>2022</t>
         </is>
       </c>
       <c r="G14" s="14" t="n">
@@ -2177,17 +2177,17 @@
       </c>
       <c r="D15" s="14" t="inlineStr">
         <is>
-          <t>Från rikt till fattigt</t>
+          <t>Från jordbrukssamhälle till industriland</t>
         </is>
       </c>
       <c r="E15" s="14" t="inlineStr">
         <is>
-          <t>Från diktatur till koloni</t>
+          <t>Från låg utbildningsnivå till hög utbildning</t>
         </is>
       </c>
       <c r="F15" s="14" t="inlineStr">
         <is>
-          <t>Från öde till obebott</t>
+          <t>Från landsbygd till urbaniserat samhälle</t>
         </is>
       </c>
       <c r="G15" s="14" t="n">
@@ -2405,17 +2405,17 @@
       </c>
       <c r="D19" s="14" t="inlineStr">
         <is>
-          <t>Gratis lyxbilar</t>
+          <t>Låga skatter generellt</t>
         </is>
       </c>
       <c r="E19" s="14" t="inlineStr">
         <is>
-          <t>Inga lagar</t>
+          <t>Privata försäkringar som huvudlösning</t>
         </is>
       </c>
       <c r="F19" s="14" t="inlineStr">
         <is>
-          <t>Evig sommar</t>
+          <t>Minimalt statligt ansvar</t>
         </is>
       </c>
       <c r="G19" s="14" t="n">
@@ -2462,17 +2462,17 @@
       </c>
       <c r="D20" s="14" t="inlineStr">
         <is>
-          <t>Land utan myndigheter</t>
+          <t>Land med svag förvaltning och korruptionsproblem</t>
         </is>
       </c>
       <c r="E20" s="14" t="inlineStr">
         <is>
-          <t>Land i ständig konflikt</t>
+          <t>Land med stora regionala skillnader</t>
         </is>
       </c>
       <c r="F20" s="14" t="inlineStr">
         <is>
-          <t>Land utan utbildning</t>
+          <t>Land med instabila institutioner</t>
         </is>
       </c>
       <c r="G20" s="14" t="n">
@@ -2519,17 +2519,17 @@
       </c>
       <c r="D21" s="14" t="inlineStr">
         <is>
-          <t>Farlig och instabil</t>
+          <t>Mindre stabil än grannländerna</t>
         </is>
       </c>
       <c r="E21" s="14" t="inlineStr">
         <is>
-          <t>Utan polis</t>
+          <t>Otrygg i vissa områden</t>
         </is>
       </c>
       <c r="F21" s="14" t="inlineStr">
         <is>
-          <t>Utan domstolar</t>
+          <t>Instabil politiskt</t>
         </is>
       </c>
       <c r="G21" s="14" t="n">
@@ -2576,17 +2576,17 @@
       </c>
       <c r="D22" s="14" t="inlineStr">
         <is>
-          <t>Den är alltid låg</t>
+          <t>Den varierar mellan olika grupper</t>
         </is>
       </c>
       <c r="E22" s="14" t="inlineStr">
         <is>
-          <t>Den saknar betydelse</t>
+          <t>Den är lägre än i andra nordiska länder</t>
         </is>
       </c>
       <c r="F22" s="14" t="inlineStr">
         <is>
-          <t>Den är okänd</t>
+          <t>Den är svår att mäta</t>
         </is>
       </c>
       <c r="G22" s="14" t="n">
@@ -2633,17 +2633,17 @@
       </c>
       <c r="D23" s="14" t="inlineStr">
         <is>
-          <t>Ökenjordbruk</t>
+          <t>Utbildning</t>
         </is>
       </c>
       <c r="E23" s="14" t="inlineStr">
         <is>
-          <t>Kärnvapenproduktion</t>
+          <t>Innovation</t>
         </is>
       </c>
       <c r="F23" s="14" t="inlineStr">
         <is>
-          <t>Rymdkolonier</t>
+          <t>Låg korruption</t>
         </is>
       </c>
       <c r="G23" s="14" t="n">
@@ -2804,17 +2804,17 @@
       </c>
       <c r="D26" s="14" t="inlineStr">
         <is>
-          <t>Det är avskaffat</t>
+          <t>Det är mer ojämlikt mellan regioner</t>
         </is>
       </c>
       <c r="E26" s="14" t="inlineStr">
         <is>
-          <t>Det är bara privat</t>
+          <t>Det finansieras främst privat</t>
         </is>
       </c>
       <c r="F26" s="14" t="inlineStr">
         <is>
-          <t>Det finns bara i städer</t>
+          <t>Det är avgiftsbelagt för de flesta</t>
         </is>
       </c>
       <c r="G26" s="14" t="n">
@@ -2861,17 +2861,17 @@
       </c>
       <c r="D27" s="14" t="inlineStr">
         <is>
-          <t>Bara kungahuset</t>
+          <t>Polis och rättsväsende</t>
         </is>
       </c>
       <c r="E27" s="14" t="inlineStr">
         <is>
-          <t>Bara armén</t>
+          <t>Riksdagen och regeringen</t>
         </is>
       </c>
       <c r="F27" s="14" t="inlineStr">
         <is>
-          <t>Inga institutioner alls</t>
+          <t>Kommuner och myndigheter</t>
         </is>
       </c>
       <c r="G27" s="14" t="n">
